--- a/output/roomself_excel/12112.xlsx
+++ b/output/roomself_excel/12112.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>371326</v>
+        <v>96367</v>
       </c>
       <c r="D2" t="n">
-        <v>8264</v>
+        <v>2532</v>
       </c>
       <c r="E2" t="n">
-        <v>818</v>
+        <v>386</v>
       </c>
       <c r="F2" t="n">
-        <v>787</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>134940</v>
+        <v>189097</v>
       </c>
       <c r="D3" t="n">
-        <v>2944</v>
+        <v>3576</v>
       </c>
       <c r="E3" t="n">
-        <v>390</v>
+        <v>570</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14214</v>
+        <v>134940</v>
       </c>
       <c r="D4" t="n">
-        <v>1076</v>
+        <v>2944</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>111482</v>
+        <v>377</v>
       </c>
       <c r="D5" t="n">
-        <v>2692</v>
+        <v>1137</v>
       </c>
       <c r="E5" t="n">
-        <v>296</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,108 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34780</v>
+        <v>111482</v>
       </c>
       <c r="D6" t="n">
-        <v>1492</v>
+        <v>2692</v>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>295</v>
       </c>
       <c r="F6" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>34780</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1492</v>
+      </c>
+      <c r="E7" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>83790</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3112</v>
+      </c>
+      <c r="E8" t="n">
+        <v>174</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1695</v>
+      </c>
+      <c r="D9" t="n">
+        <v>512</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>14214</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1076</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/12112.xlsx
+++ b/output/roomself_excel/12112.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2532</v>
       </c>
-      <c r="E2" t="n">
-        <v>386</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>279</v>
+        <v>370</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>255</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3576</v>
       </c>
-      <c r="E3" t="n">
-        <v>570</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>393</v>
+        <v>546</v>
+      </c>
+      <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>345</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2944</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>390</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>346</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +609,12 @@
       <c r="D5" t="n">
         <v>1137</v>
       </c>
-      <c r="E5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,10 +631,26 @@
       <c r="D6" t="n">
         <v>2692</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>377</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>295</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>16</v>
       </c>
     </row>
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>1492</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>185</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>16</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>3112</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>174</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>16</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,12 @@
       <c r="D9" t="n">
         <v>512</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +751,12 @@
       <c r="D10" t="n">
         <v>1076</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
